--- a/upload/lei_orcamentaria_anual.xlsx
+++ b/upload/lei_orcamentaria_anual.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{740180D0-C258-4DD5-AFB3-7E5584497D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="720" windowWidth="19200" windowHeight="15480" xr2:uid="{09D23C17-8A3B-428E-806A-DA6F0B9F0FEF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>descricao</t>
   </si>
@@ -150,13 +149,22 @@
   </si>
   <si>
     <t>https://www.almg.gov.br/atividade-parlamentar/orcamento-do-estado/loa/leis/LOA-2018</t>
+  </si>
+  <si>
+    <t>Em tramitação</t>
+  </si>
+  <si>
+    <t>Lei Orçamentária Anual - LOA 2027</t>
+  </si>
+  <si>
+    <t>https://www.almg.gov.br/atividade-parlamentar/orcamento-do-estado/loa/leis/LOA-2027</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,14 +534,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFEB01BF-438F-47FF-A719-9BF1B39B404C}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -547,123 +556,137 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>36</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>29</v>
       </c>
     </row>
